--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_04-06-2025.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_04-06-2025.xlsx
@@ -538,54 +538,54 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>£11.15</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>£11.15</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>£11.15</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>£12.00</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>£11.15</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
           <t>£11.25</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>£11.25</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>£12.12</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>£11.17</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
         <is>
           <t>£11.18</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>£12.00</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>£11.15</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>£11.25</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>£12.12</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>£11.17</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>£11.18</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>£11.18</t>
-        </is>
-      </c>
       <c r="M2" t="inlineStr">
         <is>
           <t>£16.09</t>
@@ -608,7 +608,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.directinsulation.com', port=443): Max retries exceeded with url: /product-page/celotex-tb4025-2400x1200x25mm (Caused by NewConnectionError('&lt;urllib3.connection.HTTPSConnection object at 0x000001A20DE4E210&gt;: Failed to establish a new connection: [Errno 11001] getaddrinfo failed'))</t>
+          <t>Error: HTTPSConnectionPool(host='www.directinsulation.com', port=443): Max retries exceeded with url: /product-page/celotex-tb4025-2400x1200x25mm (Caused by NewConnectionError('&lt;urllib3.connection.HTTPSConnection object at 0x000002054ED1A950&gt;: Failed to establish a new connection: [Errno 11001] getaddrinfo failed'))</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -635,54 +635,54 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>£12.80</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>£12.80</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>£12.80</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>£14.00</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>£12.80</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
           <t>£13.15</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>£13.15</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>£13.33</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
         <is>
           <t>£12.83</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>£14.00</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>£12.80</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>£13.15</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>£13.33</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>£12.84</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
         <is>
           <t>£12.83</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>£12.84</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>£12.83</t>
-        </is>
-      </c>
       <c r="M3" t="inlineStr">
         <is>
           <t>£18.88</t>
@@ -705,7 +705,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.directinsulation.com', port=443): Max retries exceeded with url: /product-page/celotex-tb4030-2400x1200x30mm (Caused by NewConnectionError('&lt;urllib3.connection.HTTPSConnection object at 0x000001A20DECA410&gt;: Failed to establish a new connection: [Errno 11001] getaddrinfo failed'))</t>
+          <t>Error: HTTPSConnectionPool(host='www.directinsulation.com', port=443): Max retries exceeded with url: /product-page/celotex-tb4030-2400x1200x30mm (Caused by NewConnectionError('&lt;urllib3.connection.HTTPSConnection object at 0x000002054F3B25D0&gt;: Failed to establish a new connection: [Errno 11001] getaddrinfo failed'))</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -732,54 +732,54 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>£16.46</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>£16.46</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>£14.46</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>£17.00</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>£16.46</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
           <t>£16.73</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>£16.73</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>£14.46</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>£17.00</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>£18.00</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
         <is>
           <t>£16.46</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>£16.73</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>£18.00</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>£15.63</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
         <is>
           <t>£16.46</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>£15.63</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>£16.46</t>
-        </is>
-      </c>
       <c r="M4" t="inlineStr">
         <is>
           <t>£22.31</t>
@@ -802,7 +802,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.directinsulation.com', port=443): Max retries exceeded with url: /product-page/celotex-tb4040-2400x1200x40mm (Caused by NewConnectionError('&lt;urllib3.connection.HTTPSConnection object at 0x000001A20DBE8590&gt;: Failed to establish a new connection: [Errno 11001] getaddrinfo failed'))</t>
+          <t>Error: HTTPSConnectionPool(host='www.directinsulation.com', port=443): Max retries exceeded with url: /product-page/celotex-tb4040-2400x1200x40mm (Caused by NewConnectionError('&lt;urllib3.connection.HTTPSConnection object at 0x00000205501ABB50&gt;: Failed to establish a new connection: [Errno 11001] getaddrinfo failed'))</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -829,54 +829,54 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>£16.70</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>£16.70</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>£16.70</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>£17.50</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>£16.70</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>£17.50</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
           <t>£17.48</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>£17.48</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>£16.75</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>£16.75</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
         <is>
           <t>£16.74</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>£17.50</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>£16.70</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>£17.50</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>£17.48</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>£16.75</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>£16.75</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>£16.74</t>
-        </is>
-      </c>
       <c r="M5" t="inlineStr">
         <is>
           <t>£23.71</t>
@@ -899,7 +899,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.directinsulation.com', port=443): Max retries exceeded with url: /product-page/celotex-ga4050-2400x1200x50mm (Caused by NewConnectionError('&lt;urllib3.connection.HTTPSConnection object at 0x000001A20EF45710&gt;: Failed to establish a new connection: [Errno 11001] getaddrinfo failed'))</t>
+          <t>Error: HTTPSConnectionPool(host='www.directinsulation.com', port=443): Max retries exceeded with url: /product-page/celotex-ga4050-2400x1200x50mm (Caused by NewConnectionError('&lt;urllib3.connection.HTTPSConnection object at 0x000002054EBD4BD0&gt;: Failed to establish a new connection: [Errno 11001] getaddrinfo failed'))</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -926,54 +926,54 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
+          <t>£21.20</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>£21.20</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>£21.20</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>£22.00</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>£21.20</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
           <t>£21.65</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>£21.65</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>£24.48</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>£21.46</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>£21.45</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
         <is>
           <t>£21.44</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>£22.00</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>£21.20</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>£21.65</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>£24.48</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>£21.46</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>£21.45</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>£21.44</t>
-        </is>
-      </c>
       <c r="M6" t="inlineStr">
         <is>
           <t>£27.93</t>
@@ -996,7 +996,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.directinsulation.com', port=443): Max retries exceeded with url: /product-page/celotex-ga4060-2400x1200x60mm (Caused by NewConnectionError('&lt;urllib3.connection.HTTPSConnection object at 0x000001A20D923490&gt;: Failed to establish a new connection: [Errno 11001] getaddrinfo failed'))</t>
+          <t>Error: HTTPSConnectionPool(host='www.directinsulation.com', port=443): Max retries exceeded with url: /product-page/celotex-ga4060-2400x1200x60mm (Caused by NewConnectionError('&lt;urllib3.connection.HTTPSConnection object at 0x00000205508AF750&gt;: Failed to establish a new connection: [Errno 11001] getaddrinfo failed'))</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1023,54 +1023,54 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
+          <t>£23.13</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>£23.13</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>£23.13</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>£25.00</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>£23.13</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
           <t>£23.44</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>£23.44</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>£24.68</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
         <is>
           <t>£23.15</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>£25.00</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>£23.13</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>£23.44</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>£24.68</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>£23.16</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
         <is>
           <t>£23.15</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>£23.16</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>£23.15</t>
-        </is>
-      </c>
       <c r="M7" t="inlineStr">
         <is>
           <t>£34.34</t>
@@ -1093,7 +1093,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.directinsulation.com', port=443): Max retries exceeded with url: /product-page/celotex-ga4070-2400x1200x70mm (Caused by NewConnectionError('&lt;urllib3.connection.HTTPSConnection object at 0x000001A20D650CD0&gt;: Failed to establish a new connection: [Errno 11001] getaddrinfo failed'))</t>
+          <t>Error: HTTPSConnectionPool(host='www.directinsulation.com', port=443): Max retries exceeded with url: /product-page/celotex-ga4070-2400x1200x70mm (Caused by NewConnectionError('&lt;urllib3.connection.HTTPSConnection object at 0x00000205508420D0&gt;: Failed to establish a new connection: [Errno 11001] getaddrinfo failed'))</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.directinsulation.com', port=443): Max retries exceeded with url: /product-page/celotex-ga4075-2400x1200x75mm (Caused by NewConnectionError('&lt;urllib3.connection.HTTPSConnection object at 0x000001A20DEEE110&gt;: Failed to establish a new connection: [Errno 11001] getaddrinfo failed'))</t>
+          <t>Error: HTTPSConnectionPool(host='www.directinsulation.com', port=443): Max retries exceeded with url: /product-page/celotex-ga4075-2400x1200x75mm (Caused by NewConnectionError('&lt;urllib3.connection.HTTPSConnection object at 0x000002054F610050&gt;: Failed to establish a new connection: [Errno 11001] getaddrinfo failed'))</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -1287,7 +1287,7 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.directinsulation.com', port=443): Max retries exceeded with url: /product-page/celotex-ga4080-2400x1200x80mm (Caused by NewConnectionError('&lt;urllib3.connection.HTTPSConnection object at 0x000001A20DAB1290&gt;: Failed to establish a new connection: [Errno 11001] getaddrinfo failed'))</t>
+          <t>Error: HTTPSConnectionPool(host='www.directinsulation.com', port=443): Max retries exceeded with url: /product-page/celotex-ga4080-2400x1200x80mm (Caused by NewConnectionError('&lt;urllib3.connection.HTTPSConnection object at 0x00000205500AC110&gt;: Failed to establish a new connection: [Errno 11001] getaddrinfo failed'))</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -1314,54 +1314,54 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
+          <t>£29.28</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>£29.28</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>£29.28</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>£30.50</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>£29.28</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
           <t>£29.36</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>£29.36</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>£31.00</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>£29.33</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>£28.43</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
         <is>
           <t>£29.31</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>£30.50</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>£29.28</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>£29.36</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>£31.00</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>£29.33</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>£28.43</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>£29.31</t>
-        </is>
-      </c>
       <c r="M10" t="inlineStr">
         <is>
           <t>£40.61</t>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.directinsulation.com', port=443): Max retries exceeded with url: /product-page/celotex-ga4090-2400x1200x90mm (Caused by NewConnectionError('&lt;urllib3.connection.HTTPSConnection object at 0x000001A20EC64310&gt;: Failed to establish a new connection: [Errno 11001] getaddrinfo failed'))</t>
+          <t>Error: HTTPSConnectionPool(host='www.directinsulation.com', port=443): Max retries exceeded with url: /product-page/celotex-ga4090-2400x1200x90mm (Caused by NewConnectionError('&lt;urllib3.connection.HTTPSConnection object at 0x000002055045F5D0&gt;: Failed to establish a new connection: [Errno 11001] getaddrinfo failed'))</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.directinsulation.com', port=443): Max retries exceeded with url: /product-page/celotex-ga4100-2400x1200x100mm (Caused by NewConnectionError('&lt;urllib3.connection.HTTPSConnection object at 0x000001A20E1B3D10&gt;: Failed to establish a new connection: [Errno 11001] getaddrinfo failed'))</t>
+          <t>Error: HTTPSConnectionPool(host='www.directinsulation.com', port=443): Max retries exceeded with url: /product-page/celotex-ga4100-2400x1200x100mm (Caused by NewConnectionError('&lt;urllib3.connection.HTTPSConnection object at 0x0000020550B18250&gt;: Failed to establish a new connection: [Errno 11001] getaddrinfo failed'))</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
@@ -1518,14 +1518,14 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
+          <t>£37.00</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
           <t>£37.50</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>£37.50</t>
-        </is>
-      </c>
       <c r="G12" t="inlineStr">
         <is>
           <t>£37.00</t>
@@ -1538,7 +1538,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>£41.18</t>
+          <t>Error: list index out of range</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.directinsulation.com', port=443): Max retries exceeded with url: /product-page/celotex-xr4110-insulation-2400x1200x110mm (Caused by NewConnectionError('&lt;urllib3.connection.HTTPSConnection object at 0x000001A20D17F210&gt;: Failed to establish a new connection: [Errno 11001] getaddrinfo failed'))</t>
+          <t>Error: HTTPSConnectionPool(host='www.directinsulation.com', port=443): Max retries exceeded with url: /product-page/celotex-xr4110-insulation-2400x1200x110mm (Caused by NewConnectionError('&lt;urllib3.connection.HTTPSConnection object at 0x00000205505BD990&gt;: Failed to establish a new connection: [Errno 11001] getaddrinfo failed'))</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -1605,54 +1605,54 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
+          <t>£35.85</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>£35.85</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>£35.08</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>£37.50</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>£35.85</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
           <t>£35.90</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>£35.90</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>£38.00</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
         <is>
           <t>£35.08</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>£37.50</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>£35.85</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>£35.90</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>£38.00</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>£35.09</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
         <is>
           <t>£35.08</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>£35.09</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>£35.08</t>
-        </is>
-      </c>
       <c r="M13" t="inlineStr">
         <is>
           <t>£52.20</t>
@@ -1675,7 +1675,7 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.directinsulation.com', port=443): Max retries exceeded with url: /product-page/celotex-xr4120-2400x1200x120mm (Caused by NewConnectionError('&lt;urllib3.connection.HTTPSConnection object at 0x000001A20EC951D0&gt;: Failed to establish a new connection: [Errno 11001] getaddrinfo failed'))</t>
+          <t>Error: HTTPSConnectionPool(host='www.directinsulation.com', port=443): Max retries exceeded with url: /product-page/celotex-xr4120-2400x1200x120mm (Caused by NewConnectionError('&lt;urllib3.connection.HTTPSConnection object at 0x000002054FFC4390&gt;: Failed to establish a new connection: [Errno 11001] getaddrinfo failed'))</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.directinsulation.com', port=443): Max retries exceeded with url: /product-page/celotex-xr4130-2400x1200x130mm (Caused by NewConnectionError('&lt;urllib3.connection.HTTPSConnection object at 0x000001A20CF11590&gt;: Failed to establish a new connection: [Errno 11001] getaddrinfo failed'))</t>
+          <t>Error: HTTPSConnectionPool(host='www.directinsulation.com', port=443): Max retries exceeded with url: /product-page/celotex-xr4130-2400x1200x130mm (Caused by NewConnectionError('&lt;urllib3.connection.HTTPSConnection object at 0x000002054F6672D0&gt;: Failed to establish a new connection: [Errno 11001] getaddrinfo failed'))</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
@@ -1869,7 +1869,7 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.directinsulation.com', port=443): Max retries exceeded with url: /product-page/celotex-xr4140-2400x1200x140mm (Caused by NewConnectionError('&lt;urllib3.connection.HTTPSConnection object at 0x000001A20C993750&gt;: Failed to establish a new connection: [Errno 11001] getaddrinfo failed'))</t>
+          <t>Error: HTTPSConnectionPool(host='www.directinsulation.com', port=443): Max retries exceeded with url: /product-page/celotex-xr4140-2400x1200x140mm (Caused by NewConnectionError('&lt;urllib3.connection.HTTPSConnection object at 0x000002054F678810&gt;: Failed to establish a new connection: [Errno 11001] getaddrinfo failed'))</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.directinsulation.com', port=443): Max retries exceeded with url: /product-page/celotex-xr4150-2400x1200x150mm (Caused by NewConnectionError('&lt;urllib3.connection.HTTPSConnection object at 0x000001A20D55D490&gt;: Failed to establish a new connection: [Errno 11001] getaddrinfo failed'))</t>
+          <t>Error: HTTPSConnectionPool(host='www.directinsulation.com', port=443): Max retries exceeded with url: /product-page/celotex-xr4150-2400x1200x150mm (Caused by NewConnectionError('&lt;urllib3.connection.HTTPSConnection object at 0x00000205510DC050&gt;: Failed to establish a new connection: [Errno 11001] getaddrinfo failed'))</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -2257,7 +2257,7 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.directinsulation.com', port=443): Max retries exceeded with url: /product-page/celotex-pl4025-ins-plasterboard-25mm-12-5mm (Caused by NewConnectionError('&lt;urllib3.connection.HTTPSConnection object at 0x000001A20E331AD0&gt;: Failed to establish a new connection: [Errno 11001] getaddrinfo failed'))</t>
+          <t>Error: HTTPSConnectionPool(host='www.directinsulation.com', port=443): Max retries exceeded with url: /product-page/celotex-pl4025-ins-plasterboard-25mm-12-5mm (Caused by NewConnectionError('&lt;urllib3.connection.HTTPSConnection object at 0x000002054F58DE50&gt;: Failed to establish a new connection: [Errno 11001] getaddrinfo failed'))</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.directinsulation.com', port=443): Max retries exceeded with url: /product-page/celotex-pl4050-ins-plasterboard-50mm-12-5mm (Caused by NewConnectionError('&lt;urllib3.connection.HTTPSConnection object at 0x000001A20EED76D0&gt;: Failed to establish a new connection: [Errno 11001] getaddrinfo failed'))</t>
+          <t>Error: HTTPSConnectionPool(host='www.directinsulation.com', port=443): Max retries exceeded with url: /product-page/celotex-pl4050-ins-plasterboard-50mm-12-5mm (Caused by NewConnectionError('&lt;urllib3.connection.HTTPSConnection object at 0x000002054F84C710&gt;: Failed to establish a new connection: [Errno 11001] getaddrinfo failed'))</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
@@ -2645,7 +2645,7 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.directinsulation.com', port=443): Max retries exceeded with url: /product-page/celotex-cavity-insulation-cw4050-450mm-x-1200mm-pack-of-11 (Caused by NewConnectionError('&lt;urllib3.connection.HTTPSConnection object at 0x000001A20D403490&gt;: Failed to establish a new connection: [Errno 11001] getaddrinfo failed'))</t>
+          <t>Error: HTTPSConnectionPool(host='www.directinsulation.com', port=443): Max retries exceeded with url: /product-page/celotex-cavity-insulation-cw4050-450mm-x-1200mm-pack-of-11 (Caused by NewConnectionError('&lt;urllib3.connection.HTTPSConnection object at 0x0000020550E9DC50&gt;: Failed to establish a new connection: [Errno 11001] getaddrinfo failed'))</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -2742,7 +2742,7 @@
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.directinsulation.com', port=443): Max retries exceeded with url: /product-page/celotex-cavity-cw4075-450mm-x-1200mm-pack-of-8 (Caused by NewConnectionError('&lt;urllib3.connection.HTTPSConnection object at 0x000001A20C9D5090&gt;: Failed to establish a new connection: [Errno 11001] getaddrinfo failed'))</t>
+          <t>Error: HTTPSConnectionPool(host='www.directinsulation.com', port=443): Max retries exceeded with url: /product-page/celotex-cavity-cw4075-450mm-x-1200mm-pack-of-8 (Caused by NewConnectionError('&lt;urllib3.connection.HTTPSConnection object at 0x000002055013C750&gt;: Failed to establish a new connection: [Errno 11001] getaddrinfo failed'))</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.directinsulation.com', port=443): Max retries exceeded with url: /product-page/celotex-cavity-cw4100-450mm-x-1200mm-pack-of-6 (Caused by NewConnectionError('&lt;urllib3.connection.HTTPSConnection object at 0x000001A20D12C050&gt;: Failed to establish a new connection: [Errno 11001] getaddrinfo failed'))</t>
+          <t>Error: HTTPSConnectionPool(host='www.directinsulation.com', port=443): Max retries exceeded with url: /product-page/celotex-cavity-cw4100-450mm-x-1200mm-pack-of-6 (Caused by NewConnectionError('&lt;urllib3.connection.HTTPSConnection object at 0x000002054F9D0C90&gt;: Failed to establish a new connection: [Errno 11001] getaddrinfo failed'))</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">

--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_04-06-2025.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_04-06-2025.xlsx
@@ -608,7 +608,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.directinsulation.com', port=443): Max retries exceeded with url: /product-page/celotex-tb4025-2400x1200x25mm (Caused by NewConnectionError('&lt;urllib3.connection.HTTPSConnection object at 0x000002054ED1A950&gt;: Failed to establish a new connection: [Errno 11001] getaddrinfo failed'))</t>
+          <t>Error: HTTPSConnectionPool(host='www.directinsulation.com', port=443): Max retries exceeded with url: /product-page/celotex-tb4025-2400x1200x25mm (Caused by NewConnectionError('&lt;urllib3.connection.HTTPSConnection object at 0x000002B36379F790&gt;: Failed to establish a new connection: [Errno 11001] getaddrinfo failed'))</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -705,7 +705,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.directinsulation.com', port=443): Max retries exceeded with url: /product-page/celotex-tb4030-2400x1200x30mm (Caused by NewConnectionError('&lt;urllib3.connection.HTTPSConnection object at 0x000002054F3B25D0&gt;: Failed to establish a new connection: [Errno 11001] getaddrinfo failed'))</t>
+          <t>Error: HTTPSConnectionPool(host='www.directinsulation.com', port=443): Max retries exceeded with url: /product-page/celotex-tb4030-2400x1200x30mm (Caused by NewConnectionError('&lt;urllib3.connection.HTTPSConnection object at 0x000002B3632E2C10&gt;: Failed to establish a new connection: [Errno 11001] getaddrinfo failed'))</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -802,7 +802,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.directinsulation.com', port=443): Max retries exceeded with url: /product-page/celotex-tb4040-2400x1200x40mm (Caused by NewConnectionError('&lt;urllib3.connection.HTTPSConnection object at 0x00000205501ABB50&gt;: Failed to establish a new connection: [Errno 11001] getaddrinfo failed'))</t>
+          <t>Error: HTTPSConnectionPool(host='www.directinsulation.com', port=443): Max retries exceeded with url: /product-page/celotex-tb4040-2400x1200x40mm (Caused by NewConnectionError('&lt;urllib3.connection.HTTPSConnection object at 0x000002B36355D890&gt;: Failed to establish a new connection: [Errno 11001] getaddrinfo failed'))</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.directinsulation.com', port=443): Max retries exceeded with url: /product-page/celotex-ga4050-2400x1200x50mm (Caused by NewConnectionError('&lt;urllib3.connection.HTTPSConnection object at 0x000002054EBD4BD0&gt;: Failed to establish a new connection: [Errno 11001] getaddrinfo failed'))</t>
+          <t>Error: HTTPSConnectionPool(host='www.directinsulation.com', port=443): Max retries exceeded with url: /product-page/celotex-ga4050-2400x1200x50mm (Caused by NewConnectionError('&lt;urllib3.connection.HTTPSConnection object at 0x000002B363D11650&gt;: Failed to establish a new connection: [Errno 11001] getaddrinfo failed'))</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.directinsulation.com', port=443): Max retries exceeded with url: /product-page/celotex-ga4060-2400x1200x60mm (Caused by NewConnectionError('&lt;urllib3.connection.HTTPSConnection object at 0x00000205508AF750&gt;: Failed to establish a new connection: [Errno 11001] getaddrinfo failed'))</t>
+          <t>Error: HTTPSConnectionPool(host='www.directinsulation.com', port=443): Max retries exceeded with url: /product-page/celotex-ga4060-2400x1200x60mm (Caused by NewConnectionError('&lt;urllib3.connection.HTTPSConnection object at 0x000002B364656ED0&gt;: Failed to establish a new connection: [Errno 11001] getaddrinfo failed'))</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1093,7 +1093,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.directinsulation.com', port=443): Max retries exceeded with url: /product-page/celotex-ga4070-2400x1200x70mm (Caused by NewConnectionError('&lt;urllib3.connection.HTTPSConnection object at 0x00000205508420D0&gt;: Failed to establish a new connection: [Errno 11001] getaddrinfo failed'))</t>
+          <t>Error: HTTPSConnectionPool(host='www.directinsulation.com', port=443): Max retries exceeded with url: /product-page/celotex-ga4070-2400x1200x70mm (Caused by NewConnectionError('&lt;urllib3.connection.HTTPSConnection object at 0x000002B363928CD0&gt;: Failed to establish a new connection: [Errno 11001] getaddrinfo failed'))</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.directinsulation.com', port=443): Max retries exceeded with url: /product-page/celotex-ga4075-2400x1200x75mm (Caused by NewConnectionError('&lt;urllib3.connection.HTTPSConnection object at 0x000002054F610050&gt;: Failed to establish a new connection: [Errno 11001] getaddrinfo failed'))</t>
+          <t>Error: HTTPSConnectionPool(host='www.directinsulation.com', port=443): Max retries exceeded with url: /product-page/celotex-ga4075-2400x1200x75mm (Caused by NewConnectionError('&lt;urllib3.connection.HTTPSConnection object at 0x000002B363025510&gt;: Failed to establish a new connection: [Errno 11001] getaddrinfo failed'))</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>£27.62</t>
+          <t>Error: list index out of range</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1287,7 +1287,7 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.directinsulation.com', port=443): Max retries exceeded with url: /product-page/celotex-ga4080-2400x1200x80mm (Caused by NewConnectionError('&lt;urllib3.connection.HTTPSConnection object at 0x00000205500AC110&gt;: Failed to establish a new connection: [Errno 11001] getaddrinfo failed'))</t>
+          <t>Error: HTTPSConnectionPool(host='www.directinsulation.com', port=443): Max retries exceeded with url: /product-page/celotex-ga4080-2400x1200x80mm (Caused by NewConnectionError('&lt;urllib3.connection.HTTPSConnection object at 0x000002B3633727D0&gt;: Failed to establish a new connection: [Errno 11001] getaddrinfo failed'))</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.directinsulation.com', port=443): Max retries exceeded with url: /product-page/celotex-ga4090-2400x1200x90mm (Caused by NewConnectionError('&lt;urllib3.connection.HTTPSConnection object at 0x000002055045F5D0&gt;: Failed to establish a new connection: [Errno 11001] getaddrinfo failed'))</t>
+          <t>Error: HTTPSConnectionPool(host='www.directinsulation.com', port=443): Max retries exceeded with url: /product-page/celotex-ga4090-2400x1200x90mm (Caused by NewConnectionError('&lt;urllib3.connection.HTTPSConnection object at 0x000002B363F8D410&gt;: Failed to establish a new connection: [Errno 11001] getaddrinfo failed'))</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.directinsulation.com', port=443): Max retries exceeded with url: /product-page/celotex-ga4100-2400x1200x100mm (Caused by NewConnectionError('&lt;urllib3.connection.HTTPSConnection object at 0x0000020550B18250&gt;: Failed to establish a new connection: [Errno 11001] getaddrinfo failed'))</t>
+          <t>Error: HTTPSConnectionPool(host='www.directinsulation.com', port=443): Max retries exceeded with url: /product-page/celotex-ga4100-2400x1200x100mm (Caused by NewConnectionError('&lt;urllib3.connection.HTTPSConnection object at 0x000002B364621110&gt;: Failed to establish a new connection: [Errno 11001] getaddrinfo failed'))</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
@@ -1538,7 +1538,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Error: list index out of range</t>
+          <t>£41.18</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.directinsulation.com', port=443): Max retries exceeded with url: /product-page/celotex-xr4110-insulation-2400x1200x110mm (Caused by NewConnectionError('&lt;urllib3.connection.HTTPSConnection object at 0x00000205505BD990&gt;: Failed to establish a new connection: [Errno 11001] getaddrinfo failed'))</t>
+          <t>Error: HTTPSConnectionPool(host='www.directinsulation.com', port=443): Max retries exceeded with url: /product-page/celotex-xr4110-insulation-2400x1200x110mm (Caused by NewConnectionError('&lt;urllib3.connection.HTTPSConnection object at 0x000002B364BD2AD0&gt;: Failed to establish a new connection: [Errno 11001] getaddrinfo failed'))</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.directinsulation.com', port=443): Max retries exceeded with url: /product-page/celotex-xr4120-2400x1200x120mm (Caused by NewConnectionError('&lt;urllib3.connection.HTTPSConnection object at 0x000002054FFC4390&gt;: Failed to establish a new connection: [Errno 11001] getaddrinfo failed'))</t>
+          <t>Error: HTTPSConnectionPool(host='www.directinsulation.com', port=443): Max retries exceeded with url: /product-page/celotex-xr4120-2400x1200x120mm (Caused by NewConnectionError('&lt;urllib3.connection.HTTPSConnection object at 0x000002B36274DA90&gt;: Failed to establish a new connection: [Errno 11001] getaddrinfo failed'))</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -1732,7 +1732,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>£46.00</t>
+          <t>Error: list index out of range</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.directinsulation.com', port=443): Max retries exceeded with url: /product-page/celotex-xr4130-2400x1200x130mm (Caused by NewConnectionError('&lt;urllib3.connection.HTTPSConnection object at 0x000002054F6672D0&gt;: Failed to establish a new connection: [Errno 11001] getaddrinfo failed'))</t>
+          <t>Error: HTTPSConnectionPool(host='www.directinsulation.com', port=443): Max retries exceeded with url: /product-page/celotex-xr4130-2400x1200x130mm (Caused by NewConnectionError('&lt;urllib3.connection.HTTPSConnection object at 0x000002B364520CD0&gt;: Failed to establish a new connection: [Errno 11001] getaddrinfo failed'))</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
@@ -1869,7 +1869,7 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.directinsulation.com', port=443): Max retries exceeded with url: /product-page/celotex-xr4140-2400x1200x140mm (Caused by NewConnectionError('&lt;urllib3.connection.HTTPSConnection object at 0x000002054F678810&gt;: Failed to establish a new connection: [Errno 11001] getaddrinfo failed'))</t>
+          <t>Error: HTTPSConnectionPool(host='www.directinsulation.com', port=443): Max retries exceeded with url: /product-page/celotex-xr4140-2400x1200x140mm (Caused by NewConnectionError('&lt;urllib3.connection.HTTPSConnection object at 0x000002B36392F090&gt;: Failed to establish a new connection: [Errno 11001] getaddrinfo failed'))</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.directinsulation.com', port=443): Max retries exceeded with url: /product-page/celotex-xr4150-2400x1200x150mm (Caused by NewConnectionError('&lt;urllib3.connection.HTTPSConnection object at 0x00000205510DC050&gt;: Failed to establish a new connection: [Errno 11001] getaddrinfo failed'))</t>
+          <t>Error: HTTPSConnectionPool(host='www.directinsulation.com', port=443): Max retries exceeded with url: /product-page/celotex-xr4150-2400x1200x150mm (Caused by NewConnectionError('&lt;urllib3.connection.HTTPSConnection object at 0x000002B363D26590&gt;: Failed to establish a new connection: [Errno 11001] getaddrinfo failed'))</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -2257,7 +2257,7 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.directinsulation.com', port=443): Max retries exceeded with url: /product-page/celotex-pl4025-ins-plasterboard-25mm-12-5mm (Caused by NewConnectionError('&lt;urllib3.connection.HTTPSConnection object at 0x000002054F58DE50&gt;: Failed to establish a new connection: [Errno 11001] getaddrinfo failed'))</t>
+          <t>Error: HTTPSConnectionPool(host='www.directinsulation.com', port=443): Max retries exceeded with url: /product-page/celotex-pl4025-ins-plasterboard-25mm-12-5mm (Caused by NewConnectionError('&lt;urllib3.connection.HTTPSConnection object at 0x000002B3627ADED0&gt;: Failed to establish a new connection: [Errno 11001] getaddrinfo failed'))</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.directinsulation.com', port=443): Max retries exceeded with url: /product-page/celotex-pl4050-ins-plasterboard-50mm-12-5mm (Caused by NewConnectionError('&lt;urllib3.connection.HTTPSConnection object at 0x000002054F84C710&gt;: Failed to establish a new connection: [Errno 11001] getaddrinfo failed'))</t>
+          <t>Error: HTTPSConnectionPool(host='www.directinsulation.com', port=443): Max retries exceeded with url: /product-page/celotex-pl4050-ins-plasterboard-50mm-12-5mm (Caused by NewConnectionError('&lt;urllib3.connection.HTTPSConnection object at 0x000002B36488D890&gt;: Failed to establish a new connection: [Errno 11001] getaddrinfo failed'))</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
@@ -2645,7 +2645,7 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.directinsulation.com', port=443): Max retries exceeded with url: /product-page/celotex-cavity-insulation-cw4050-450mm-x-1200mm-pack-of-11 (Caused by NewConnectionError('&lt;urllib3.connection.HTTPSConnection object at 0x0000020550E9DC50&gt;: Failed to establish a new connection: [Errno 11001] getaddrinfo failed'))</t>
+          <t>Error: HTTPSConnectionPool(host='www.directinsulation.com', port=443): Max retries exceeded with url: /product-page/celotex-cavity-insulation-cw4050-450mm-x-1200mm-pack-of-11 (Caused by NewConnectionError('&lt;urllib3.connection.HTTPSConnection object at 0x000002B3644D4350&gt;: Failed to establish a new connection: [Errno 11001] getaddrinfo failed'))</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -2742,7 +2742,7 @@
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.directinsulation.com', port=443): Max retries exceeded with url: /product-page/celotex-cavity-cw4075-450mm-x-1200mm-pack-of-8 (Caused by NewConnectionError('&lt;urllib3.connection.HTTPSConnection object at 0x000002055013C750&gt;: Failed to establish a new connection: [Errno 11001] getaddrinfo failed'))</t>
+          <t>Error: HTTPSConnectionPool(host='www.directinsulation.com', port=443): Max retries exceeded with url: /product-page/celotex-cavity-cw4075-450mm-x-1200mm-pack-of-8 (Caused by NewConnectionError('&lt;urllib3.connection.HTTPSConnection object at 0x000002B362DFA610&gt;: Failed to establish a new connection: [Errno 11001] getaddrinfo failed'))</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.directinsulation.com', port=443): Max retries exceeded with url: /product-page/celotex-cavity-cw4100-450mm-x-1200mm-pack-of-6 (Caused by NewConnectionError('&lt;urllib3.connection.HTTPSConnection object at 0x000002054F9D0C90&gt;: Failed to establish a new connection: [Errno 11001] getaddrinfo failed'))</t>
+          <t>Error: HTTPSConnectionPool(host='www.directinsulation.com', port=443): Max retries exceeded with url: /product-page/celotex-cavity-cw4100-450mm-x-1200mm-pack-of-6 (Caused by NewConnectionError('&lt;urllib3.connection.HTTPSConnection object at 0x000002B364336CD0&gt;: Failed to establish a new connection: [Errno 11001] getaddrinfo failed'))</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
